--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/136.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/136.xlsx
@@ -426,13 +426,13 @@
         <v>-4.847257742962091</v>
       </c>
       <c r="E2">
-        <v>-18.93357525173075</v>
+        <v>-15.21998549884664</v>
       </c>
       <c r="F2">
-        <v>-0.6353405494792698</v>
+        <v>-0.5235606521455045</v>
       </c>
       <c r="G2">
-        <v>-11.87121436704309</v>
+        <v>-13.15833755790785</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.0676653269189</v>
       </c>
       <c r="E3">
-        <v>-20.18048142815006</v>
+        <v>-16.42869459071149</v>
       </c>
       <c r="F3">
-        <v>-1.128074189849486</v>
+        <v>-0.07332143117150039</v>
       </c>
       <c r="G3">
-        <v>-12.38864175367272</v>
+        <v>-12.80271237268476</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.437386882129775</v>
       </c>
       <c r="E4">
-        <v>-21.14778511175924</v>
+        <v>-17.10232885475338</v>
       </c>
       <c r="F4">
-        <v>-0.9879674408095885</v>
+        <v>-0.1429556517856324</v>
       </c>
       <c r="G4">
-        <v>-12.76393759401754</v>
+        <v>-12.70173790950657</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.916242571681415</v>
       </c>
       <c r="E5">
-        <v>-22.05694383682084</v>
+        <v>-17.70871016781232</v>
       </c>
       <c r="F5">
-        <v>-0.67921337223374</v>
+        <v>-0.04978088631874404</v>
       </c>
       <c r="G5">
-        <v>-12.19235553233445</v>
+        <v>-13.15921476809046</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.474859510619622</v>
       </c>
       <c r="E6">
-        <v>-23.42516531603838</v>
+        <v>-18.89371688264638</v>
       </c>
       <c r="F6">
-        <v>-0.1984504692013797</v>
+        <v>0.1291845775864779</v>
       </c>
       <c r="G6">
-        <v>-12.49805283799709</v>
+        <v>-13.61381980762413</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.085262896848683</v>
       </c>
       <c r="E7">
-        <v>-23.83542783712759</v>
+        <v>-18.97567220171922</v>
       </c>
       <c r="F7">
-        <v>-0.8106404876271039</v>
+        <v>0.5068132538680914</v>
       </c>
       <c r="G7">
-        <v>-12.71580982285267</v>
+        <v>-13.72307685801763</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.720633853895013</v>
       </c>
       <c r="E8">
-        <v>-24.64527497298988</v>
+        <v>-20.19965680483679</v>
       </c>
       <c r="F8">
-        <v>0.6946902942926304</v>
+        <v>0.5998695627963795</v>
       </c>
       <c r="G8">
-        <v>-12.4106216123853</v>
+        <v>-13.57056499123857</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.338128316357848</v>
       </c>
       <c r="E9">
-        <v>-25.45589045294727</v>
+        <v>-20.32915393394494</v>
       </c>
       <c r="F9">
-        <v>0.1631617233471053</v>
+        <v>0.9908026479343557</v>
       </c>
       <c r="G9">
-        <v>-12.31563228118223</v>
+        <v>-13.79429013822943</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.904864537447766</v>
       </c>
       <c r="E10">
-        <v>-25.96000309034363</v>
+        <v>-21.29804414428022</v>
       </c>
       <c r="F10">
-        <v>0.05966632840873784</v>
+        <v>1.271996933019065</v>
       </c>
       <c r="G10">
-        <v>-13.2665503104649</v>
+        <v>-13.40060812910168</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.394394129100517</v>
       </c>
       <c r="E11">
-        <v>-27.75058124202829</v>
+        <v>-22.34456202748786</v>
       </c>
       <c r="F11">
-        <v>0.2779784155795336</v>
+        <v>1.529012830350862</v>
       </c>
       <c r="G11">
-        <v>-11.232883398399</v>
+        <v>-13.12904630896785</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.777460744102871</v>
       </c>
       <c r="E12">
-        <v>-27.18697800561508</v>
+        <v>-22.33829067838737</v>
       </c>
       <c r="F12">
-        <v>1.347280619320289</v>
+        <v>1.790367716138523</v>
       </c>
       <c r="G12">
-        <v>-11.17242769127489</v>
+        <v>-13.31234668670992</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.02896004117647</v>
       </c>
       <c r="E13">
-        <v>-30.93954772338837</v>
+        <v>-24.99956051184306</v>
       </c>
       <c r="F13">
-        <v>1.043970581315639</v>
+        <v>2.186898908184618</v>
       </c>
       <c r="G13">
-        <v>-12.88593246727109</v>
+        <v>-12.72800722158235</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.1468549361858</v>
       </c>
       <c r="E14">
-        <v>-29.02042768120027</v>
+        <v>-24.58455917663222</v>
       </c>
       <c r="F14">
-        <v>1.027100050790224</v>
+        <v>2.271195231828301</v>
       </c>
       <c r="G14">
-        <v>-11.155295985268</v>
+        <v>-12.87125747192444</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.1313315012551</v>
       </c>
       <c r="E15">
-        <v>-30.07306947450638</v>
+        <v>-26.76515294419754</v>
       </c>
       <c r="F15">
-        <v>1.190661194472987</v>
+        <v>2.44419148022895</v>
       </c>
       <c r="G15">
-        <v>-12.14890360473226</v>
+        <v>-12.54508018031681</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.986511814791497</v>
       </c>
       <c r="E16">
-        <v>-31.367351332508</v>
+        <v>-26.23908643173813</v>
       </c>
       <c r="F16">
-        <v>1.798348207697093</v>
+        <v>2.846587513486866</v>
       </c>
       <c r="G16">
-        <v>-10.4386753131979</v>
+        <v>-11.27315674446151</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.741922824915974</v>
       </c>
       <c r="E17">
-        <v>-31.35494153706941</v>
+        <v>-27.58053631075583</v>
       </c>
       <c r="F17">
-        <v>2.206478200117187</v>
+        <v>3.150296824579665</v>
       </c>
       <c r="G17">
-        <v>-10.40608930458393</v>
+        <v>-10.70257198721223</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.428906780759053</v>
       </c>
       <c r="E18">
-        <v>-32.30353292705459</v>
+        <v>-28.44701248303216</v>
       </c>
       <c r="F18">
-        <v>2.179962159553575</v>
+        <v>3.727715292905478</v>
       </c>
       <c r="G18">
-        <v>-9.449384559915053</v>
+        <v>-9.873597921663572</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.07179642480561</v>
       </c>
       <c r="E19">
-        <v>-33.35096036354237</v>
+        <v>-29.3532016619965</v>
       </c>
       <c r="F19">
-        <v>2.494105586452037</v>
+        <v>3.894598189873466</v>
       </c>
       <c r="G19">
-        <v>-9.328799488740712</v>
+        <v>-9.512294366954814</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.707787848236681</v>
       </c>
       <c r="E20">
-        <v>-36.00261758938674</v>
+        <v>-30.31493173600777</v>
       </c>
       <c r="F20">
-        <v>2.878368657262671</v>
+        <v>4.499260005342548</v>
       </c>
       <c r="G20">
-        <v>-8.36387742547131</v>
+        <v>-8.796768902240691</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.368114389684106</v>
       </c>
       <c r="E21">
-        <v>-35.60179739424452</v>
+        <v>-31.20490262474866</v>
       </c>
       <c r="F21">
-        <v>2.968746854377709</v>
+        <v>4.642287577844717</v>
       </c>
       <c r="G21">
-        <v>-8.873056164565318</v>
+        <v>-8.834850528218965</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.066288235833973</v>
       </c>
       <c r="E22">
-        <v>-35.82103503705391</v>
+        <v>-32.52003775681224</v>
       </c>
       <c r="F22">
-        <v>3.352219662686073</v>
+        <v>5.040704134099584</v>
       </c>
       <c r="G22">
-        <v>-8.830878280323587</v>
+        <v>-8.612062638536313</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.811316679266225</v>
       </c>
       <c r="E23">
-        <v>-37.90879830169234</v>
+        <v>-32.72940944611949</v>
       </c>
       <c r="F23">
-        <v>3.470381302491005</v>
+        <v>5.25317540271324</v>
       </c>
       <c r="G23">
-        <v>-7.104137029250442</v>
+        <v>-7.974542306087769</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.613903870894</v>
       </c>
       <c r="E24">
-        <v>-37.45290860098856</v>
+        <v>-33.98444761031281</v>
       </c>
       <c r="F24">
-        <v>4.56312713209839</v>
+        <v>5.512431205502207</v>
       </c>
       <c r="G24">
-        <v>-7.440416597053379</v>
+        <v>-6.755955076856618</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.466457805886115</v>
       </c>
       <c r="E25">
-        <v>-36.54576626002517</v>
+        <v>-34.21074986558573</v>
       </c>
       <c r="F25">
-        <v>4.258541408293429</v>
+        <v>5.468822631949229</v>
       </c>
       <c r="G25">
-        <v>-7.136134314959126</v>
+        <v>-7.295340130869805</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.351835627615071</v>
       </c>
       <c r="E26">
-        <v>-38.08888777455389</v>
+        <v>-33.94483428069659</v>
       </c>
       <c r="F26">
-        <v>3.896577987966157</v>
+        <v>6.405825449421473</v>
       </c>
       <c r="G26">
-        <v>-6.152504961322102</v>
+        <v>-7.390595758021164</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.268996796845704</v>
       </c>
       <c r="E27">
-        <v>-38.82467484607184</v>
+        <v>-34.86015637136423</v>
       </c>
       <c r="F27">
-        <v>4.01222470433619</v>
+        <v>6.305148988754833</v>
       </c>
       <c r="G27">
-        <v>-7.806748445844622</v>
+        <v>-7.641182856109991</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.202629260249741</v>
       </c>
       <c r="E28">
-        <v>-40.57522434700779</v>
+        <v>-35.34567300505368</v>
       </c>
       <c r="F28">
-        <v>4.648122597830036</v>
+        <v>5.857749411237625</v>
       </c>
       <c r="G28">
-        <v>-7.522020640737807</v>
+        <v>-7.961901080777598</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.130522055279958</v>
       </c>
       <c r="E29">
-        <v>-39.67863323941513</v>
+        <v>-35.10688411993266</v>
       </c>
       <c r="F29">
-        <v>4.220047175085336</v>
+        <v>5.887711460196884</v>
       </c>
       <c r="G29">
-        <v>-7.021611392725351</v>
+        <v>-6.863713559854819</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.048515870733075</v>
       </c>
       <c r="E30">
-        <v>-39.05309731572608</v>
+        <v>-35.0326869996146</v>
       </c>
       <c r="F30">
-        <v>4.057660656379743</v>
+        <v>5.775684709377084</v>
       </c>
       <c r="G30">
-        <v>-6.645873031172327</v>
+        <v>-7.999217758590676</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.948538005951137</v>
       </c>
       <c r="E31">
-        <v>-40.55265164345735</v>
+        <v>-34.31925043484121</v>
       </c>
       <c r="F31">
-        <v>4.029822541441263</v>
+        <v>5.60848040585681</v>
       </c>
       <c r="G31">
-        <v>-6.743428724308457</v>
+        <v>-7.228834023155786</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.817773622184601</v>
       </c>
       <c r="E32">
-        <v>-37.91260264326588</v>
+        <v>-34.27945021071537</v>
       </c>
       <c r="F32">
-        <v>3.242026917296071</v>
+        <v>5.25627349679971</v>
       </c>
       <c r="G32">
-        <v>-8.82764878926438</v>
+        <v>-7.735678756585337</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.657273572143434</v>
       </c>
       <c r="E33">
-        <v>-37.85456359160706</v>
+        <v>-33.98451198508834</v>
       </c>
       <c r="F33">
-        <v>3.747876098754812</v>
+        <v>4.922570658786346</v>
       </c>
       <c r="G33">
-        <v>-6.453403718426273</v>
+        <v>-7.646536187894069</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.47051345827994</v>
       </c>
       <c r="E34">
-        <v>-37.70837470618442</v>
+        <v>-34.48020606312928</v>
       </c>
       <c r="F34">
-        <v>3.603432017993856</v>
+        <v>5.131541246755772</v>
       </c>
       <c r="G34">
-        <v>-5.408333101581989</v>
+        <v>-8.062147146214871</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.254850742557132</v>
       </c>
       <c r="E35">
-        <v>-37.38269441033101</v>
+        <v>-33.52039061953875</v>
       </c>
       <c r="F35">
-        <v>3.016111245734979</v>
+        <v>4.875227804981549</v>
       </c>
       <c r="G35">
-        <v>-6.465783869277332</v>
+        <v>-7.345696172543199</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.010708529808775</v>
       </c>
       <c r="E36">
-        <v>-38.15647090583716</v>
+        <v>-33.34290521017787</v>
       </c>
       <c r="F36">
-        <v>2.884841520148147</v>
+        <v>4.401928492248412</v>
       </c>
       <c r="G36">
-        <v>-6.88064684927278</v>
+        <v>-7.33191144110212</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.746354569590103</v>
       </c>
       <c r="E37">
-        <v>-36.53912735172243</v>
+        <v>-32.35171225502826</v>
       </c>
       <c r="F37">
-        <v>2.945608896082713</v>
+        <v>4.426093626122879</v>
       </c>
       <c r="G37">
-        <v>-7.012296256024259</v>
+        <v>-6.827841929172923</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.462170360193427</v>
       </c>
       <c r="E38">
-        <v>-37.09407737234036</v>
+        <v>-31.60652646628223</v>
       </c>
       <c r="F38">
-        <v>2.851817825268142</v>
+        <v>4.349673419745013</v>
       </c>
       <c r="G38">
-        <v>-6.305708675417812</v>
+        <v>-7.057062693528078</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.154851333806381</v>
       </c>
       <c r="E39">
-        <v>-38.66939873427047</v>
+        <v>-31.45074573930489</v>
       </c>
       <c r="F39">
-        <v>2.672931884633589</v>
+        <v>3.682009293088612</v>
       </c>
       <c r="G39">
-        <v>-7.032184908319359</v>
+        <v>-7.292262062996882</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.83240666451252</v>
       </c>
       <c r="E40">
-        <v>-35.63781819606476</v>
+        <v>-30.02936315512955</v>
       </c>
       <c r="F40">
-        <v>3.351807135719479</v>
+        <v>3.414822700785243</v>
       </c>
       <c r="G40">
-        <v>-7.097714597556303</v>
+        <v>-6.662874199949656</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.495148776933233</v>
       </c>
       <c r="E41">
-        <v>-34.09723014044419</v>
+        <v>-30.82739232816704</v>
       </c>
       <c r="F41">
-        <v>1.851456498625375</v>
+        <v>3.325198318006753</v>
       </c>
       <c r="G41">
-        <v>-4.909850583077774</v>
+        <v>-6.227005168974111</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.140142670599601</v>
       </c>
       <c r="E42">
-        <v>-33.63003332190856</v>
+        <v>-30.1875568978866</v>
       </c>
       <c r="F42">
-        <v>2.200883406678679</v>
+        <v>3.290049032371164</v>
       </c>
       <c r="G42">
-        <v>-5.992333169912711</v>
+        <v>-5.856911237227074</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.772320023852421</v>
       </c>
       <c r="E43">
-        <v>-34.46212921083796</v>
+        <v>-29.60256877636186</v>
       </c>
       <c r="F43">
-        <v>2.282639955865379</v>
+        <v>3.096525839729144</v>
       </c>
       <c r="G43">
-        <v>-6.092564876254732</v>
+        <v>-5.860944837620344</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.393556045723782</v>
       </c>
       <c r="E44">
-        <v>-33.64545834876898</v>
+        <v>-28.9625132258812</v>
       </c>
       <c r="F44">
-        <v>2.421285464806738</v>
+        <v>2.62277755186369</v>
       </c>
       <c r="G44">
-        <v>-4.895342675384957</v>
+        <v>-5.669363178035269</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.002636276554391</v>
       </c>
       <c r="E45">
-        <v>-33.97809527359148</v>
+        <v>-29.5386259348048</v>
       </c>
       <c r="F45">
-        <v>2.079457999306717</v>
+        <v>3.338324627871514</v>
       </c>
       <c r="G45">
-        <v>-5.584678455733327</v>
+        <v>-6.190094461944951</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.603077312778026</v>
       </c>
       <c r="E46">
-        <v>-34.37088315803148</v>
+        <v>-29.84005562973254</v>
       </c>
       <c r="F46">
-        <v>2.869876234649171</v>
+        <v>2.579291576686327</v>
       </c>
       <c r="G46">
-        <v>-5.921976213926799</v>
+        <v>-5.399699369219177</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.201500983476781</v>
       </c>
       <c r="E47">
-        <v>-33.12017886985562</v>
+        <v>-27.30665278994001</v>
       </c>
       <c r="F47">
-        <v>2.543517702029027</v>
+        <v>2.683165535527773</v>
       </c>
       <c r="G47">
-        <v>-4.847576492345949</v>
+        <v>-5.291865174627834</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.802718097664509</v>
       </c>
       <c r="E48">
-        <v>-31.93503717565351</v>
+        <v>-27.44539496745724</v>
       </c>
       <c r="F48">
-        <v>1.240424537828764</v>
+        <v>2.543348715078857</v>
       </c>
       <c r="G48">
-        <v>-6.033076450001625</v>
+        <v>-5.277563515757715</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.413110980971886</v>
       </c>
       <c r="E49">
-        <v>-32.17971946764446</v>
+        <v>-26.3169300715994</v>
       </c>
       <c r="F49">
-        <v>1.714214244064358</v>
+        <v>2.4291450147245</v>
       </c>
       <c r="G49">
-        <v>-5.054731243417015</v>
+        <v>-5.3128216214607</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.045128375591101</v>
       </c>
       <c r="E50">
-        <v>-31.05596431342898</v>
+        <v>-26.89338749706295</v>
       </c>
       <c r="F50">
-        <v>1.319281801105666</v>
+        <v>2.313490014680438</v>
       </c>
       <c r="G50">
-        <v>-5.675843046110412</v>
+        <v>-5.499048643889402</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.7070863673031254</v>
       </c>
       <c r="E51">
-        <v>-30.80855336159762</v>
+        <v>-25.12355048273449</v>
       </c>
       <c r="F51">
-        <v>2.16235769550928</v>
+        <v>2.393415871906952</v>
       </c>
       <c r="G51">
-        <v>-5.283549953105139</v>
+        <v>-5.336665551811338</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.4055332141435679</v>
       </c>
       <c r="E52">
-        <v>-30.45535388750589</v>
+        <v>-25.6229533784885</v>
       </c>
       <c r="F52">
-        <v>1.304932820954373</v>
+        <v>2.156125059170616</v>
       </c>
       <c r="G52">
-        <v>-5.210161922648944</v>
+        <v>-5.057208840033981</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.1521516082736637</v>
       </c>
       <c r="E53">
-        <v>-29.06758116597672</v>
+        <v>-25.07982962711802</v>
       </c>
       <c r="F53">
-        <v>1.260529014694708</v>
+        <v>2.155303318707039</v>
       </c>
       <c r="G53">
-        <v>-6.053476808236584</v>
+        <v>-4.79369072398537</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.04657199586353562</v>
       </c>
       <c r="E54">
-        <v>-29.21483742670983</v>
+        <v>-24.5533104146242</v>
       </c>
       <c r="F54">
-        <v>0.6570327121613649</v>
+        <v>1.822173710936412</v>
       </c>
       <c r="G54">
-        <v>-4.768298622092202</v>
+        <v>-4.647953739420244</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.1875950585181609</v>
       </c>
       <c r="E55">
-        <v>-28.17278009246506</v>
+        <v>-23.50463286152765</v>
       </c>
       <c r="F55">
-        <v>1.00565196199694</v>
+        <v>1.543820726043306</v>
       </c>
       <c r="G55">
-        <v>-5.713302009503705</v>
+        <v>-5.618847880941818</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.265902244760496</v>
       </c>
       <c r="E56">
-        <v>-26.50680658694791</v>
+        <v>-22.8322943994191</v>
       </c>
       <c r="F56">
-        <v>0.8086678503460228</v>
+        <v>1.768197290969997</v>
       </c>
       <c r="G56">
-        <v>-5.628651226881448</v>
+        <v>-5.608621594378427</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.2806587470563947</v>
       </c>
       <c r="E57">
-        <v>-28.07106379390868</v>
+        <v>-22.87940012226531</v>
       </c>
       <c r="F57">
-        <v>1.42469652331632</v>
+        <v>1.335092021355498</v>
       </c>
       <c r="G57">
-        <v>-4.189963869524196</v>
+        <v>-5.70083570408114</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.2359797126648772</v>
       </c>
       <c r="E58">
-        <v>-25.72507253854338</v>
+        <v>-22.38813336749664</v>
       </c>
       <c r="F58">
-        <v>1.329546929961158</v>
+        <v>1.48107686548566</v>
       </c>
       <c r="G58">
-        <v>-5.847092226819897</v>
+        <v>-5.946746958607282</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.1370680663840587</v>
       </c>
       <c r="E59">
-        <v>-25.8784007942334</v>
+        <v>-21.83697315221262</v>
       </c>
       <c r="F59">
-        <v>0.889246461085942</v>
+        <v>1.172732010406794</v>
       </c>
       <c r="G59">
-        <v>-5.95445648738484</v>
+        <v>-6.232331087939982</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.007272817772622017</v>
       </c>
       <c r="E60">
-        <v>-24.70437101693087</v>
+        <v>-21.79312770025641</v>
       </c>
       <c r="F60">
-        <v>0.8181062685335204</v>
+        <v>1.524910754972199</v>
       </c>
       <c r="G60">
-        <v>-5.770443376369402</v>
+        <v>-6.06317572439257</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.1829713354830745</v>
       </c>
       <c r="E61">
-        <v>-26.22084137438816</v>
+        <v>-20.71806894882454</v>
       </c>
       <c r="F61">
-        <v>0.9823897485915239</v>
+        <v>0.9617451761789546</v>
       </c>
       <c r="G61">
-        <v>-6.56785876130068</v>
+        <v>-6.333395621806568</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.3737923566529994</v>
       </c>
       <c r="E62">
-        <v>-26.65007161159787</v>
+        <v>-20.28974826489497</v>
       </c>
       <c r="F62">
-        <v>1.087042372791602</v>
+        <v>1.188156211446921</v>
       </c>
       <c r="G62">
-        <v>-6.507070184241198</v>
+        <v>-6.742486245511064</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.5629422158916686</v>
       </c>
       <c r="E63">
-        <v>-24.40371589591521</v>
+        <v>-19.21411221708895</v>
       </c>
       <c r="F63">
-        <v>0.6722108880828602</v>
+        <v>0.4788235476948989</v>
       </c>
       <c r="G63">
-        <v>-6.569158912107054</v>
+        <v>-6.916889205686615</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.7332200174011514</v>
       </c>
       <c r="E64">
-        <v>-24.4275013371725</v>
+        <v>-19.75946624294086</v>
       </c>
       <c r="F64">
-        <v>0.6137389182214515</v>
+        <v>0.4073810010404555</v>
       </c>
       <c r="G64">
-        <v>-5.616247579329069</v>
+        <v>-7.594479246119565</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.8694031046421945</v>
       </c>
       <c r="E65">
-        <v>-21.17122168326526</v>
+        <v>-19.53868983533562</v>
       </c>
       <c r="F65">
-        <v>1.023483398709602</v>
+        <v>0.6925820992525057</v>
       </c>
       <c r="G65">
-        <v>-7.960067032702341</v>
+        <v>-7.182028594126306</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.9575638861203791</v>
       </c>
       <c r="E66">
-        <v>-23.51623278075789</v>
+        <v>-19.68906100456237</v>
       </c>
       <c r="F66">
-        <v>-0.03924819479214833</v>
+        <v>0.2333807713476138</v>
       </c>
       <c r="G66">
-        <v>-7.302261214780847</v>
+        <v>-7.026422995006772</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.9861643885389381</v>
       </c>
       <c r="E67">
-        <v>-25.15226578583435</v>
+        <v>-19.00229428631137</v>
       </c>
       <c r="F67">
-        <v>-0.07320048953069166</v>
+        <v>0.3092037248280609</v>
       </c>
       <c r="G67">
-        <v>-6.226083576133448</v>
+        <v>-6.752681203139362</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.9488161448094864</v>
       </c>
       <c r="E68">
-        <v>-24.5480566022983</v>
+        <v>-19.87331822498838</v>
       </c>
       <c r="F68">
-        <v>-0.04755920494443577</v>
+        <v>0.3304231842181731</v>
       </c>
       <c r="G68">
-        <v>-6.837713154471922</v>
+        <v>-7.250385719755426</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.8390224464395692</v>
       </c>
       <c r="E69">
-        <v>-22.70082449493166</v>
+        <v>-18.8647150079651</v>
       </c>
       <c r="F69">
-        <v>-0.1059094047976329</v>
+        <v>-0.4077275531098412</v>
       </c>
       <c r="G69">
-        <v>-6.871738988727901</v>
+        <v>-7.149553542157448</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.6540148933450717</v>
       </c>
       <c r="E70">
-        <v>-23.27981953251468</v>
+        <v>-18.62118730872245</v>
       </c>
       <c r="F70">
-        <v>-0.1585521532455415</v>
+        <v>-0.2829431159195265</v>
       </c>
       <c r="G70">
-        <v>-6.233550305664032</v>
+        <v>-6.776295387965982</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.3970982049537501</v>
       </c>
       <c r="E71">
-        <v>-23.15661867177496</v>
+        <v>-19.0898522874614</v>
       </c>
       <c r="F71">
-        <v>-0.2754099427584678</v>
+        <v>-0.70397410227082</v>
       </c>
       <c r="G71">
-        <v>-6.472825047439565</v>
+        <v>-7.158834739178856</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.07129939862505112</v>
       </c>
       <c r="E72">
-        <v>-23.24093301488031</v>
+        <v>-18.323846450344</v>
       </c>
       <c r="F72">
-        <v>-1.057066536081512</v>
+        <v>-0.3662586525582952</v>
       </c>
       <c r="G72">
-        <v>-7.08178383406133</v>
+        <v>-6.732628073935021</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>0.3180688190541657</v>
       </c>
       <c r="E73">
-        <v>-24.97592873940478</v>
+        <v>-18.78333283205508</v>
       </c>
       <c r="F73">
-        <v>-0.7749560766493069</v>
+        <v>-0.2106688883926724</v>
       </c>
       <c r="G73">
-        <v>-5.768968305675423</v>
+        <v>-6.605818987655467</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.7612305759888864</v>
       </c>
       <c r="E74">
-        <v>-23.64092464436322</v>
+        <v>-20.16158846983341</v>
       </c>
       <c r="F74">
-        <v>-1.207887389109218</v>
+        <v>-0.8196539533369653</v>
       </c>
       <c r="G74">
-        <v>-5.801654827956161</v>
+        <v>-5.896108956518049</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>1.247674930677149</v>
       </c>
       <c r="E75">
-        <v>-23.62323611733078</v>
+        <v>-19.40032560004896</v>
       </c>
       <c r="F75">
-        <v>0.1195730306117953</v>
+        <v>-0.8276833185723009</v>
       </c>
       <c r="G75">
-        <v>-5.377139925207367</v>
+        <v>-5.698204073533297</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>1.768051389768142</v>
       </c>
       <c r="E76">
-        <v>-24.12947935213678</v>
+        <v>-19.74698999612108</v>
       </c>
       <c r="F76">
-        <v>-1.430800228835162</v>
+        <v>-1.148660776543859</v>
       </c>
       <c r="G76">
-        <v>-4.316926989734626</v>
+        <v>-5.400372941323685</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>2.30901637327805</v>
       </c>
       <c r="E77">
-        <v>-23.00250130593323</v>
+        <v>-20.4227714704179</v>
       </c>
       <c r="F77">
-        <v>-0.9524205388206561</v>
+        <v>-0.9418472572913232</v>
       </c>
       <c r="G77">
-        <v>-4.718838065813562</v>
+        <v>-4.819829498831597</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>2.854279756938409</v>
       </c>
       <c r="E78">
-        <v>-24.42363885064041</v>
+        <v>-21.12608042937569</v>
       </c>
       <c r="F78">
-        <v>-0.9894303376429324</v>
+        <v>-0.8851322546912523</v>
       </c>
       <c r="G78">
-        <v>-4.040342097007494</v>
+        <v>-4.838893155835906</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>3.39278323757107</v>
       </c>
       <c r="E79">
-        <v>-24.34162538660902</v>
+        <v>-21.32676360059141</v>
       </c>
       <c r="F79">
-        <v>-1.176036662471577</v>
+        <v>-1.226500804650123</v>
       </c>
       <c r="G79">
-        <v>-2.973067097415792</v>
+        <v>-4.051552634281735</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>3.912270696065916</v>
       </c>
       <c r="E80">
-        <v>-23.92089677298124</v>
+        <v>-21.19581284751956</v>
       </c>
       <c r="F80">
-        <v>-0.9461340586008107</v>
+        <v>-1.348103482646285</v>
       </c>
       <c r="G80">
-        <v>-3.279090746152318</v>
+        <v>-3.770370220329651</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>4.395832332250523</v>
       </c>
       <c r="E81">
-        <v>-28.32177654874328</v>
+        <v>-21.77820105875497</v>
       </c>
       <c r="F81">
-        <v>-1.25376983118288</v>
+        <v>-1.208067144835625</v>
       </c>
       <c r="G81">
-        <v>-2.826533835750376</v>
+        <v>-3.354812782272968</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>4.835521979800327</v>
       </c>
       <c r="E82">
-        <v>-25.92517426017362</v>
+        <v>-23.42433882698474</v>
       </c>
       <c r="F82">
-        <v>-1.89308059837626</v>
+        <v>-1.065015549678776</v>
       </c>
       <c r="G82">
-        <v>-2.826515560538239</v>
+        <v>-3.105089840643799</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>5.222456495395275</v>
       </c>
       <c r="E83">
-        <v>-25.51052594792539</v>
+        <v>-24.2354028537652</v>
       </c>
       <c r="F83">
-        <v>-2.066338610876193</v>
+        <v>-1.172139193841405</v>
       </c>
       <c r="G83">
-        <v>-2.09204000620952</v>
+        <v>-2.190049968904504</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>5.545844960299493</v>
       </c>
       <c r="E84">
-        <v>-29.70671885675458</v>
+        <v>-24.9610270171713</v>
       </c>
       <c r="F84">
-        <v>-1.50079727437172</v>
+        <v>-1.124305946534151</v>
       </c>
       <c r="G84">
-        <v>-1.365425403844644</v>
+        <v>-2.491622298113182</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>5.800229480451267</v>
       </c>
       <c r="E85">
-        <v>-30.72806412612244</v>
+        <v>-26.53570047813474</v>
       </c>
       <c r="F85">
-        <v>-0.8624192488738927</v>
+        <v>-1.149273768421931</v>
       </c>
       <c r="G85">
-        <v>-2.42884172293068</v>
+        <v>-2.649172901953095</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>5.981958347087152</v>
       </c>
       <c r="E86">
-        <v>-29.32641344895136</v>
+        <v>-27.3263390116197</v>
       </c>
       <c r="F86">
-        <v>-1.249534388652366</v>
+        <v>-1.090424063024845</v>
       </c>
       <c r="G86">
-        <v>-1.231710898121595</v>
+        <v>-1.4919107577949</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>6.085545028910637</v>
       </c>
       <c r="E87">
-        <v>-30.8559643454762</v>
+        <v>-28.9087166795907</v>
       </c>
       <c r="F87">
-        <v>-1.284264520382138</v>
+        <v>-1.044270744810468</v>
       </c>
       <c r="G87">
-        <v>-1.301921652410404</v>
+        <v>-1.752277705122037</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>6.105342928820334</v>
       </c>
       <c r="E88">
-        <v>-30.99816407142134</v>
+        <v>-30.12314059023851</v>
       </c>
       <c r="F88">
-        <v>-1.709704078051131</v>
+        <v>-1.128499970694525</v>
       </c>
       <c r="G88">
-        <v>-2.430661411910687</v>
+        <v>-1.916757225106765</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>6.040727349856891</v>
       </c>
       <c r="E89">
-        <v>-32.73985269599577</v>
+        <v>-31.12815543267715</v>
       </c>
       <c r="F89">
-        <v>-1.416364270106575</v>
+        <v>-0.9246959102163594</v>
       </c>
       <c r="G89">
-        <v>-2.496859451762955</v>
+        <v>-1.798994368835418</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>5.888294027826132</v>
       </c>
       <c r="E90">
-        <v>-36.09136963879266</v>
+        <v>-33.40825183716272</v>
       </c>
       <c r="F90">
-        <v>-1.243414410280483</v>
+        <v>-0.9784163646553102</v>
       </c>
       <c r="G90">
-        <v>-1.212608079948419</v>
+        <v>-1.764629137782594</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>5.644191607171348</v>
       </c>
       <c r="E91">
-        <v>-35.31725257995787</v>
+        <v>-34.42056387189908</v>
       </c>
       <c r="F91">
-        <v>-1.527570108830201</v>
+        <v>-0.9010518194382532</v>
       </c>
       <c r="G91">
-        <v>-2.369893720807934</v>
+        <v>-2.24953578441302</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>5.31046706023404</v>
       </c>
       <c r="E92">
-        <v>-37.57698371271214</v>
+        <v>-35.42842574070088</v>
       </c>
       <c r="F92">
-        <v>-1.382458363942589</v>
+        <v>-0.5154890401726261</v>
       </c>
       <c r="G92">
-        <v>-1.296410370578564</v>
+        <v>-2.052108667688442</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>4.88785474454394</v>
       </c>
       <c r="E93">
-        <v>-39.88032148777145</v>
+        <v>-38.27082542645499</v>
       </c>
       <c r="F93">
-        <v>-0.8514748587481056</v>
+        <v>-0.6500192198568771</v>
       </c>
       <c r="G93">
-        <v>-2.794591375678105</v>
+        <v>-2.231983748526965</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>4.377771359374507</v>
       </c>
       <c r="E94">
-        <v>-40.54483322313836</v>
+        <v>-39.66172966932308</v>
       </c>
       <c r="F94">
-        <v>-0.7134680210743052</v>
+        <v>-0.2890465269433533</v>
       </c>
       <c r="G94">
-        <v>-1.535471031297625</v>
+        <v>-2.231341505357552</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>3.788751617476399</v>
       </c>
       <c r="E95">
-        <v>-41.0699860291063</v>
+        <v>-41.67277689097493</v>
       </c>
       <c r="F95">
-        <v>-2.086392557330567</v>
+        <v>0.09050976028457464</v>
       </c>
       <c r="G95">
-        <v>-3.511781190069063</v>
+        <v>-3.279411867737025</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>3.125153390890559</v>
       </c>
       <c r="E96">
-        <v>-45.66424555396935</v>
+        <v>-43.74078332934114</v>
       </c>
       <c r="F96">
-        <v>-1.968893611447873</v>
+        <v>0.07754415369595677</v>
       </c>
       <c r="G96">
-        <v>-2.969722733594576</v>
+        <v>-2.766815663973251</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>2.405730773527501</v>
       </c>
       <c r="E97">
-        <v>-46.43723916914077</v>
+        <v>-44.29473657924111</v>
       </c>
       <c r="F97">
-        <v>-1.446023136596409</v>
+        <v>0.2897876212738433</v>
       </c>
       <c r="G97">
-        <v>-3.305934422038145</v>
+        <v>-3.768869042189761</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>1.628150430368157</v>
       </c>
       <c r="E98">
-        <v>-47.64136311570302</v>
+        <v>-47.10025990164207</v>
       </c>
       <c r="F98">
-        <v>-0.5367101562975438</v>
+        <v>0.2449804000890152</v>
       </c>
       <c r="G98">
-        <v>-4.036653114900251</v>
+        <v>-4.480986179840185</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.8352716045055771</v>
       </c>
       <c r="E99">
-        <v>-49.42532520174722</v>
+        <v>-49.34488684311077</v>
       </c>
       <c r="F99">
-        <v>-0.2824171026187488</v>
+        <v>0.4231365490417021</v>
       </c>
       <c r="G99">
-        <v>-4.994417821873116</v>
+        <v>-4.473086066707476</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.005895284999062536</v>
       </c>
       <c r="E100">
-        <v>-51.34287325344886</v>
+        <v>-50.82078759404431</v>
       </c>
       <c r="F100">
-        <v>-0.2790067140214232</v>
+        <v>0.691274935490888</v>
       </c>
       <c r="G100">
-        <v>-4.272588714343749</v>
+        <v>-5.379500038317734</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.7828923227173157</v>
       </c>
       <c r="E101">
-        <v>-52.22479833355073</v>
+        <v>-53.74858457275671</v>
       </c>
       <c r="F101">
-        <v>0.7413812229514246</v>
+        <v>1.188489215142847</v>
       </c>
       <c r="G101">
-        <v>-5.548347334003394</v>
+        <v>-4.934420300424741</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.611440297128057</v>
       </c>
       <c r="E102">
-        <v>-55.18269259643133</v>
+        <v>-55.28816132141969</v>
       </c>
       <c r="F102">
-        <v>-0.3122863744288934</v>
+        <v>1.594536691912303</v>
       </c>
       <c r="G102">
-        <v>-5.189416946127958</v>
+        <v>-5.783236024865857</v>
       </c>
     </row>
   </sheetData>
